--- a/multi_group_attendance_export.xlsx
+++ b/multi_group_attendance_export.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10g1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12G2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12G3" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +52,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -64,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -79,6 +85,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -469,6 +478,15 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,27 +517,27 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>04/30</t>
+          <t>05/04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>05/04</t>
+          <t>05/05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>05/05</t>
+          <t>05/06</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>05/06</t>
+          <t>05/13</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>05/14</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -534,63 +552,108 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>07/29</t>
+          <t>05/20</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>05/22</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>05/26</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>07/28</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>07/30</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>08/03</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>08/04</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>08/05</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>08/06</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>08/07</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>08/11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>08/12</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>08/13</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>08/17</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>08/18</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>08/19</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>08/20</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>08/31</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FREDRIECH</t>
+          <t>OA1307001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PRETORIUS, FREDRIECH</t>
+          <t>ARENDS, ONEILL</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>10g1</t>
+          <t>12G2</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -615,9 +678,9 @@
           <t>P</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
@@ -665,7 +728,52 @@
           <t>P</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC2" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -674,43 +782,43 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AA0304012</t>
+          <t>BB1308005</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ADONIS, AMBER</t>
+          <t>BARNARD, BENJAMIN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>10g1</t>
+          <t>12G2</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -718,14 +826,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
@@ -733,14 +841,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
@@ -748,22 +856,67 @@
           <t>A</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -772,33 +925,33 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AA0304021</t>
+          <t>IB0308002</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ava, ADONIS</t>
+          <t>BOTES, IVOR</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10g1</t>
+          <t>12G2</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -806,9 +959,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -816,34 +969,34 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
@@ -856,12 +1009,6827 @@
           <t>A</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CC1503026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>COX, CHRISTIAN</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>AD2704008</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>DOUBELL, AIDAN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>JD0402008</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DWYER, JADE</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ZE1712001</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ELCHEMILY, ZAIN</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>JF0611008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>FLANAGAN, JAMIE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BG0206002</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>GEDULD, BEURAN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BH0303005</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>HAMID, BRIAN</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AJ2904015</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>JANTJIES, ANDREA</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>KK1506011</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>KOCKOTT, KALYN</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AA13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CM1710010</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>MAGGOTT, CRAIG</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AP1407031</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>PEET, AARON</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DP2305007</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>PRINSLOO, DARIUS</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SL1909006</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>LANG, SKYLAR</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>MS2709019</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SAMPSON, MATTHEW</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>LS1103031</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SCHWARTZ, LOGAN</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>NS0204011</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SMITH, NEALE</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>AV0809016</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>VISSER, ARNO</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CV0809011</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>VISSER, CHRISTIAAN</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>DH1709004</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>HARTMAN, DAWID</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12G2</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total Days Absent</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total Days Late</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>05/04</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>05/05</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>05/06</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>05/13</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>05/14</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>05/15</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>05/18</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>05/19</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>05/20</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>05/22</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>05/26</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>07/27</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>07/28</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>08/03</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>08/04</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>08/05</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>08/06</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>08/07</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>08/11</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>08/13</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>08/14</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>08/17</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>08/19</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>08/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LB1205018</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>BEROWSKY, LIAM</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X2" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ME2505003</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>EIMAN, MATTHEW</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>HE2509001</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ENGELBRECHT, HEINRICH</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y4" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>QV1106001</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>VAN WYK, QUINTON</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>DS1205010</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SWARTZ, DEACON</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SP0902012</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PIETERSE, SAMANTHA</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MV0606014</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>VOS, MICAELA LEIGH</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>MJ0610018</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>JACOBSZ, MILANDRIE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AM1902173</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>MATTHYSEN, ARNE</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB10" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LD1302007</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>DU PLESSIS, LUKA</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>PV0412002</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>VAN NIEKERK, PATRIC</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BE2412004</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ELLIS, BEN</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ZA1104006</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ADONIS, ZEPHYR</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>BW3001004</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>WOLMARANS, BIANCA</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TM1806016</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>MORGAN, TIAGO</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>DH2506005</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>HONIBALL, DANIEL</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SC2502017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>COOPER, SEAN</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AA18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>DV1202006</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>VAN DER LINDE, DEON</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BM1109011</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>MYBURGH, BIANDRI</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>AS1308031</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>STEENEKAMP, ALEXA</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>KP0309005</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>PETERSEN, KEIRHA</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>JB3112008</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>BEUKES, JESSE MAE</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>JD1010008</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>DE LANGE, JADE</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X24" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z24" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC24" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>AL2612014</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>LE ROUX, ANNIKE</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GD2511002</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>DUCKWORTH, GEMMA</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z26" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB26" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC26" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CW2910014</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>WAHL, CHRISTIAAN</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X27" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z27" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AC27" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PL2301001</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>LEGORJUS, PHILLIP</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>12G3</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Y28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Z28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AB28" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC28" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
